--- a/artfynd/A 23099-2024 artfynd.xlsx
+++ b/artfynd/A 23099-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>112992675</v>
       </c>
       <c r="B2" t="n">
-        <v>44412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102021</v>
+        <v>102018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>

--- a/artfynd/A 23099-2024 artfynd.xlsx
+++ b/artfynd/A 23099-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112992675</v>
       </c>
       <c r="B2" t="n">
-        <v>44858</v>
+        <v>44861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23099-2024 artfynd.xlsx
+++ b/artfynd/A 23099-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112992675</v>
       </c>
       <c r="B2" t="n">
-        <v>44862</v>
+        <v>45001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23099-2024 artfynd.xlsx
+++ b/artfynd/A 23099-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112992675</v>
       </c>
       <c r="B2" t="n">
-        <v>45001</v>
+        <v>45004</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23099-2024 artfynd.xlsx
+++ b/artfynd/A 23099-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112992675</v>
       </c>
       <c r="B2" t="n">
-        <v>45004</v>
+        <v>45005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23099-2024 artfynd.xlsx
+++ b/artfynd/A 23099-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112992675</v>
       </c>
       <c r="B2" t="n">
-        <v>45039</v>
+        <v>45040</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23099-2024 artfynd.xlsx
+++ b/artfynd/A 23099-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112992675</v>
       </c>
       <c r="B2" t="n">
-        <v>45040</v>
+        <v>45044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23099-2024 artfynd.xlsx
+++ b/artfynd/A 23099-2024 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>112992675</v>
       </c>
       <c r="B2" t="n">
-        <v>45044</v>
+        <v>45050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
